--- a/event.xlsx
+++ b/event.xlsx
@@ -11,7 +11,64 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="135">
+  <si>
+    <t>Polines</t>
+  </si>
+  <si>
+    <t>\Banner\Polines.png</t>
+  </si>
+  <si>
+    <t>pending</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>2026-05-03 13:22:59.751541</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>Komputer</t>
+  </si>
+  <si>
+    <t>\Banner\Komputer.png</t>
+  </si>
+  <si>
+    <t>2026-05-03 13:24:21.346342</t>
+  </si>
+  <si>
+    <t>Elektro</t>
+  </si>
+  <si>
+    <t>\Banner\Elektro.png</t>
+  </si>
+  <si>
+    <t>2026-05-03 13:24:43.839152</t>
+  </si>
+  <si>
+    <t>Desain</t>
+  </si>
+  <si>
+    <t>\Banner\Desain.png</t>
+  </si>
+  <si>
+    <t>2026-05-03 13:25:11.905427</t>
+  </si>
+  <si>
+    <t>2026-05-03 13:26:13.259295</t>
+  </si>
+  <si>
+    <t>2026-05-03 13:26:34.463114</t>
+  </si>
+  <si>
+    <t>2026-05-03 13:26:48.543139</t>
+  </si>
+  <si>
+    <t>2026-05-03 13:27:02.723376</t>
+  </si>
   <si>
     <t>SEMINAR NASIONAL Pharmacy Informatics</t>
   </si>
@@ -19,28 +76,16 @@
     <t>seminar-nasional-pharmacy-informatics</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>2026-04-23 07:57:40.853</t>
-  </si>
-  <si>
-    <t>true</t>
+    <t>2026-04-23 00:57:40.853</t>
   </si>
   <si>
     <t>https://eventkampus.com/event/detail/4493/seminar-nasional-pharmacy-informatics</t>
   </si>
   <si>
-    <t>false</t>
-  </si>
-  <si>
     <t>published</t>
   </si>
   <si>
-    <t>https://eventkampus.com/event/kategori/seminar</t>
-  </si>
-  <si>
-    <t>2026-04-23 07:57:40.916</t>
+    <t>2026-05-05 00:44:52.634282</t>
   </si>
   <si>
     <t>seminar</t>
@@ -55,6 +100,9 @@
     <t>https://eventkampus.com/event/detail/4486/tech-outlook-2024-elevating-recruitment-in-the-cloud-era</t>
   </si>
   <si>
+    <t>2026-05-05 00:44:52.644116</t>
+  </si>
+  <si>
     <t>WEBINAR KESETARAAN GENDER</t>
   </si>
   <si>
@@ -64,6 +112,9 @@
     <t>https://eventkampus.com/event/detail/4481/webinar-kesetaraan-gender</t>
   </si>
   <si>
+    <t>2026-05-05 00:44:52.647942</t>
+  </si>
+  <si>
     <t>WEBINAR NASIONAL EKSPEDISI SERIBU PULAU #4 2023</t>
   </si>
   <si>
@@ -73,6 +124,9 @@
     <t>https://eventkampus.com/event/detail/4442/webinar-nasional-ekspedisi-seribu-pulau-4-2023</t>
   </si>
   <si>
+    <t>2026-05-05 00:44:52.651251</t>
+  </si>
+  <si>
     <t>WEBINAR KESENIAN DAN KESEHATAN "ENDORFIN"</t>
   </si>
   <si>
@@ -82,6 +136,9 @@
     <t>https://eventkampus.com/event/detail/4432/webinar-kesenian-dan-kesehatan-endorfin</t>
   </si>
   <si>
+    <t>2026-05-05 00:44:52.654351</t>
+  </si>
+  <si>
     <t>Devfest Bogor 2022 “Move Together for Further”</t>
   </si>
   <si>
@@ -91,18 +148,24 @@
     <t>https://eventkampus.com/event/detail/4429/devfest-bogor-2022-move-together-for-further</t>
   </si>
   <si>
+    <t>2026-05-05 00:44:52.657992</t>
+  </si>
+  <si>
     <t>The Art of Arranging Music with</t>
   </si>
   <si>
     <t>the-art-of-arranging-music-with</t>
   </si>
   <si>
-    <t>2026-04-23 07:57:40.854</t>
+    <t>2026-04-23 00:57:40.854</t>
   </si>
   <si>
     <t>https://eventkampus.com/event/detail/4425/the-art-of-arranging-music-with</t>
   </si>
   <si>
+    <t>2026-05-05 00:44:52.662158</t>
+  </si>
+  <si>
     <t>SEMINAR NASIONAL FISIOTERAPI UNIVERSITAS AIRLANGGA 2022</t>
   </si>
   <si>
@@ -112,6 +175,9 @@
     <t>https://eventkampus.com/event/detail/4419/seminar-nasional-fisioterapi-universitas-airlangga-2022</t>
   </si>
   <si>
+    <t>2026-05-05 00:44:52.66514</t>
+  </si>
+  <si>
     <t>The 72nd MarkPlus Goes to Campus</t>
   </si>
   <si>
@@ -121,6 +187,9 @@
     <t>https://eventkampus.com/event/detail/4418/the-72nd-markplus-goes-to-campus</t>
   </si>
   <si>
+    <t>2026-05-05 00:44:52.668103</t>
+  </si>
+  <si>
     <t>Go Scholarship 2022</t>
   </si>
   <si>
@@ -130,6 +199,9 @@
     <t>https://eventkampus.com/event/detail/4414/go-scholarship-2022</t>
   </si>
   <si>
+    <t>2026-05-05 00:44:52.671362</t>
+  </si>
+  <si>
     <t>The 7th Annual International Conference and Exhibition on Indonesian Medical Education and Research </t>
   </si>
   <si>
@@ -139,6 +211,9 @@
     <t>https://eventkampus.com/event/detail/4405/the-7th-annual-international-conference-and-exhibition-on-indonesian-medical-education-and-research-institute</t>
   </si>
   <si>
+    <t>2026-05-05 00:44:52.675273</t>
+  </si>
+  <si>
     <t>ILSA Connect 2022</t>
   </si>
   <si>
@@ -148,6 +223,9 @@
     <t>https://eventkampus.com/event/detail/4399/ilsa-connect-2022</t>
   </si>
   <si>
+    <t>2026-05-05 00:44:52.679299</t>
+  </si>
+  <si>
     <t>The 69th MarkPlus Goes to Campus</t>
   </si>
   <si>
@@ -157,18 +235,24 @@
     <t>https://eventkampus.com/event/detail/4397/the-69th-markplus-goes-to-campus</t>
   </si>
   <si>
+    <t>2026-05-05 00:44:52.682593</t>
+  </si>
+  <si>
     <t>SEMINAR NASIONAL TL EXPO 2022</t>
   </si>
   <si>
     <t>seminar-nasional-tl-expo-2022</t>
   </si>
   <si>
-    <t>2026-04-23 07:57:40.86</t>
+    <t>2026-04-23 00:57:40.86</t>
   </si>
   <si>
     <t>https://eventkampus.com/event/detail/4395/seminar-nasional-tl-expo-2022</t>
   </si>
   <si>
+    <t>2026-05-05 00:44:52.685431</t>
+  </si>
+  <si>
     <t>68th MarkPlus Goes to Campus</t>
   </si>
   <si>
@@ -178,18 +262,24 @@
     <t>https://eventkampus.com/event/detail/4392/68th-markplus-goes-to-campus</t>
   </si>
   <si>
+    <t>2026-05-05 00:44:52.688281</t>
+  </si>
+  <si>
     <t>𝐌𝐀𝐍𝐀𝐆𝐄𝐌𝐄𝐍𝐓 𝐍𝐀𝐓𝐈𝐎𝐍𝐀𝐋 𝐄𝐍𝐓𝐑𝐄𝐏𝐑𝐄𝐍𝐄𝐔𝐑 𝐓𝐀𝐋𝐊 𝟐𝟎𝟐𝟐</t>
   </si>
   <si>
     <t>----</t>
   </si>
   <si>
-    <t>2026-04-23 07:57:40.861</t>
+    <t>2026-04-23 00:57:40.861</t>
   </si>
   <si>
     <t>https://eventkampus.com/event/detail/4390</t>
   </si>
   <si>
+    <t>2026-05-05 00:44:52.692441</t>
+  </si>
+  <si>
     <t>Pekan Raya Biologi 2022</t>
   </si>
   <si>
@@ -199,6 +289,9 @@
     <t>https://eventkampus.com/event/detail/4385/pekan-raya-biologi-2022</t>
   </si>
   <si>
+    <t>2026-05-05 00:44:52.695272</t>
+  </si>
+  <si>
     <t>BRAWIJAYA LAW FAIR XIII 2022: SEMINAR HUKUM NASIONAL</t>
   </si>
   <si>
@@ -208,6 +301,9 @@
     <t>https://eventkampus.com/event/detail/4377/brawijaya-law-fair-xiii-2022-seminar-hukum-nasional</t>
   </si>
   <si>
+    <t>2026-05-05 00:44:52.69805</t>
+  </si>
+  <si>
     <t>The 64th MarkPlus Goes to Campus</t>
   </si>
   <si>
@@ -217,18 +313,24 @@
     <t>https://eventkampus.com/event/detail/4371/the-64th-markplus-goes-to-campus</t>
   </si>
   <si>
+    <t>2026-05-05 00:44:52.701457</t>
+  </si>
+  <si>
     <t>The 63rd MarkPlus Goes to Campus “Entrepreneurial Marketing"</t>
   </si>
   <si>
     <t>the-63rd-markplus-goes-to-campus-entrepreneurial-marketing</t>
   </si>
   <si>
-    <t>2026-04-23 07:57:40.862</t>
+    <t>2026-04-23 00:57:40.862</t>
   </si>
   <si>
     <t>https://eventkampus.com/event/detail/4366/the-63rd-markplus-goes-to-campus-entrepreneurial-marketing</t>
   </si>
   <si>
+    <t>2026-05-05 00:44:52.704287</t>
+  </si>
+  <si>
     <t>Webinar Nasional</t>
   </si>
   <si>
@@ -238,6 +340,9 @@
     <t>https://eventkampus.com/event/detail/4363/webinar-nasional</t>
   </si>
   <si>
+    <t>2026-05-05 00:44:52.707674</t>
+  </si>
+  <si>
     <t>SPEXPERIENCE II</t>
   </si>
   <si>
@@ -247,6 +352,9 @@
     <t>https://eventkampus.com/event/detail/4361/spexperience-ii</t>
   </si>
   <si>
+    <t>2026-05-05 00:44:52.710687</t>
+  </si>
+  <si>
     <t>The 62nd MarkPlus Goes to Campus “Entrepreneurial Marketing"</t>
   </si>
   <si>
@@ -256,6 +364,9 @@
     <t>https://eventkampus.com/event/detail/4360/the-62nd-markplus-goes-to-campus-entrepreneurial-marketing</t>
   </si>
   <si>
+    <t>2026-05-05 00:44:52.714175</t>
+  </si>
+  <si>
     <t>LAWFERENCE</t>
   </si>
   <si>
@@ -265,37 +376,46 @@
     <t>https://eventkampus.com/event/detail/4358/lawference</t>
   </si>
   <si>
+    <t>2026-05-05 00:44:52.71743</t>
+  </si>
+  <si>
     <t>Event Tags</t>
   </si>
   <si>
     <t>event-tags</t>
   </si>
   <si>
+    <t>2026-05-01 20:30:41.646</t>
+  </si>
+  <si>
+    <t>https://eventkampus.com/event/tags/piagam-penghargaan</t>
+  </si>
+  <si>
+    <t>2026-05-05 00:44:52.72086</t>
+  </si>
+  <si>
+    <t>The 7th Annual International Conference and Exhibition on Indonesian Medical  Education and Research Institute</t>
+  </si>
+  <si>
+    <t>the-7th-annual-international-conference-and-exhibition-on-indonesian-medical-education-and-research-institute</t>
+  </si>
+  <si>
+    <t>online &amp; offline</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>2026-05-05 00:44:52.724061</t>
+  </si>
+  <si>
+    <t>event-tags-238</t>
+  </si>
+  <si>
     <t>2026-05-02 03:30:41.646</t>
   </si>
   <si>
-    <t>https://eventkampus.com/event/tags/piagam-penghargaan</t>
-  </si>
-  <si>
-    <t>The 7th Annual International Conference and Exhibition on Indonesian Medical  Education and Research Institute</t>
-  </si>
-  <si>
-    <t>the-7th-annual-international-conference-and-exhibition-on-indonesian-medical-education-and-research-institute</t>
-  </si>
-  <si>
-    <t>online &amp; offline</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>event-tags-238</t>
-  </si>
-  <si>
-    <t>2026-05-02 10:30:41.646</t>
-  </si>
-  <si>
-    <t>2026-05-02 10:30:41.646226</t>
+    <t>2026-05-05 00:44:52.727008</t>
   </si>
 </sst>
 </file>
@@ -671,8 +791,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{330d35cd-beaf-4fbf-a0dd-ed2ee49550c8}">
-  <dimension ref="A1:AG28"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ce6fc980-44b3-410f-982f-1b5ec58c0834}">
+  <dimension ref="A1:AG36"/>
   <sheetFormatPr baseColWidth="12" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -682,31 +802,31 @@
     <col min="5" max="5" width="50" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="50" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="50" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="20" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="31" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="31" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="20" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="50" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="21" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="22" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="31" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="21" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="17" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="10" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="50" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="31" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="21" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="26" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="22" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="22" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="19" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="17" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="18" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="31" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="31" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -748,127 +868,127 @@
       </c>
       <c r="H1" t="inlineStr" s="1">
         <is>
+          <t>banner_url</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr" s="1">
+        <is>
+          <t>tanggal_mulai</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr" s="1">
+        <is>
+          <t>tanggal_selesai</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr" s="1">
+        <is>
+          <t>detail_lokasi</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr" s="1">
+        <is>
+          <t>link_eksternal</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr" s="1">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr" s="1">
+        <is>
+          <t>hasil_scraping</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr" s="1">
+        <is>
+          <t>website_sumber</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr" s="1">
+        <is>
+          <t>jumlah_tayangan</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr" s="1">
+        <is>
+          <t>alasan_penolakan</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr" s="1">
+        <is>
+          <t>dibuat_pada</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr" s="1">
+        <is>
+          <t>diperbarui_pada</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr" s="1">
+        <is>
           <t>syarat_dan_ketentuan</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr" s="1">
-        <is>
-          <t>banner_url</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr" s="1">
-        <is>
-          <t>tanggal_mulai</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr" s="1">
-        <is>
-          <t>tanggal_selesai</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr" s="1">
+      <c r="U1" t="inlineStr" s="1">
         <is>
           <t>batas_registrasi</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr" s="1">
+      <c r="V1" t="inlineStr" s="1">
         <is>
           <t>is_event_polines</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr" s="1">
+      <c r="W1" t="inlineStr" s="1">
+        <is>
+          <t>jenis_event</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr" s="1">
         <is>
           <t>tipe_platform</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr" s="1">
+      <c r="Y1" t="inlineStr" s="1">
         <is>
           <t>tipe_harga</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr" s="1">
-        <is>
-          <t>detail_lokasi</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr" s="1">
-        <is>
-          <t>link_eksternal</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr" s="1">
+      <c r="Z1" t="inlineStr" s="1">
+        <is>
+          <t>harga</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr" s="1">
         <is>
           <t>nama_kontak</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr" s="1">
+      <c r="AB1" t="inlineStr" s="1">
         <is>
           <t>email_kontak</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr" s="1">
+      <c r="AC1" t="inlineStr" s="1">
         <is>
           <t>telepon_kontak</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr" s="1">
+      <c r="AD1" t="inlineStr" s="1">
+        <is>
+          <t>kuota</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr" s="1">
         <is>
           <t>maks_tiket_per_transaksi</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr" s="1">
+      <c r="AF1" t="inlineStr" s="1">
         <is>
           <t>satu_akun_satu_transaksi</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr" s="1">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr" s="1">
-        <is>
-          <t>hasil_scraping</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr" s="1">
-        <is>
-          <t>website_sumber</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr" s="1">
-        <is>
-          <t>jumlah_tayangan</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr" s="1">
-        <is>
-          <t>alasan_penolakan</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr" s="1">
-        <is>
-          <t>dibuat_pada</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr" s="1">
-        <is>
-          <t>diperbarui_pada</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr" s="1">
-        <is>
-          <t>jenis_event</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr" s="1">
-        <is>
-          <t>harga</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr" s="1">
-        <is>
-          <t>kuota</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr" s="1">
@@ -884,44 +1004,29 @@
       <c r="E2" t="s">
         <v>0</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>1</v>
       </c>
-      <c r="I2" t="s">
+      <c r="M2" t="s">
         <v>2</v>
       </c>
-      <c r="J2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="R2" t="s">
         <v>4</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="V2" t="s">
         <v>5</v>
       </c>
-      <c r="V2" t="s">
-        <v>6</v>
-      </c>
-      <c r="W2" t="s">
-        <v>7</v>
-      </c>
-      <c r="X2" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>8</v>
-      </c>
       <c r="Z2">
-        <v>99</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:33">
@@ -929,46 +1034,31 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M3" t="s">
         <v>2</v>
       </c>
-      <c r="J3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>13</v>
+      <c r="N3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="R3" t="s">
+        <v>8</v>
       </c>
       <c r="V3" t="s">
-        <v>6</v>
-      </c>
-      <c r="W3" t="s">
-        <v>7</v>
-      </c>
-      <c r="X3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z3">
-        <v>88</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:33">
@@ -976,46 +1066,31 @@
         <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M4" t="s">
         <v>2</v>
       </c>
-      <c r="J4" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>16</v>
+      <c r="N4" t="s">
+        <v>3</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="R4" t="s">
+        <v>11</v>
       </c>
       <c r="V4" t="s">
-        <v>6</v>
-      </c>
-      <c r="W4" t="s">
-        <v>7</v>
-      </c>
-      <c r="X4" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z4">
         <v>0</v>
       </c>
-      <c r="AB4" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
+      <c r="AF4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:33">
@@ -1023,46 +1098,31 @@
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" t="s">
+        <v>13</v>
+      </c>
+      <c r="M5" t="s">
         <v>2</v>
       </c>
-      <c r="J5" t="s">
-        <v>3</v>
-      </c>
-      <c r="M5" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>19</v>
+      <c r="N5" t="s">
+        <v>3</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="R5" t="s">
+        <v>14</v>
       </c>
       <c r="V5" t="s">
-        <v>6</v>
-      </c>
-      <c r="W5" t="s">
-        <v>7</v>
-      </c>
-      <c r="X5" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z5">
-        <v>77</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:33">
@@ -1070,46 +1130,31 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" t="s">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M6" t="s">
         <v>2</v>
       </c>
-      <c r="J6" t="s">
-        <v>3</v>
-      </c>
-      <c r="M6" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>22</v>
+      <c r="N6" t="s">
+        <v>3</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="R6" t="s">
+        <v>15</v>
       </c>
       <c r="V6" t="s">
-        <v>6</v>
-      </c>
-      <c r="W6" t="s">
-        <v>7</v>
-      </c>
-      <c r="X6" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Z6">
         <v>0</v>
       </c>
-      <c r="AB6" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
+      <c r="AF6" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:33">
@@ -1117,46 +1162,31 @@
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" t="s">
+        <v>7</v>
+      </c>
+      <c r="M7" t="s">
         <v>2</v>
       </c>
-      <c r="J7" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>25</v>
+      <c r="N7" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="R7" t="s">
+        <v>16</v>
       </c>
       <c r="V7" t="s">
-        <v>6</v>
-      </c>
-      <c r="W7" t="s">
-        <v>7</v>
-      </c>
-      <c r="X7" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Z7">
         <v>0</v>
       </c>
-      <c r="AB7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
+      <c r="AF7" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:33">
@@ -1164,46 +1194,31 @@
         <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" t="s">
-        <v>27</v>
-      </c>
-      <c r="I8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" t="s">
+        <v>10</v>
+      </c>
+      <c r="M8" t="s">
         <v>2</v>
       </c>
-      <c r="J8" t="s">
-        <v>28</v>
-      </c>
-      <c r="M8" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>29</v>
+      <c r="N8" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="R8" t="s">
+        <v>17</v>
       </c>
       <c r="V8" t="s">
-        <v>6</v>
-      </c>
-      <c r="W8" t="s">
-        <v>7</v>
-      </c>
-      <c r="X8" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Z8">
         <v>0</v>
       </c>
-      <c r="AB8" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
+      <c r="AF8" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:33">
@@ -1211,46 +1226,31 @@
         <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" t="s">
+        <v>13</v>
+      </c>
+      <c r="M9" t="s">
         <v>2</v>
       </c>
-      <c r="J9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M9" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>32</v>
+      <c r="N9" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="R9" t="s">
+        <v>18</v>
       </c>
       <c r="V9" t="s">
-        <v>6</v>
-      </c>
-      <c r="W9" t="s">
-        <v>7</v>
-      </c>
-      <c r="X9" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Z9">
         <v>0</v>
       </c>
-      <c r="AB9" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
+      <c r="AF9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:33">
@@ -1258,46 +1258,40 @@
         <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I10" t="s">
-        <v>2</v>
-      </c>
-      <c r="J10" t="s">
-        <v>28</v>
+        <v>21</v>
+      </c>
+      <c r="L10" t="s">
+        <v>22</v>
       </c>
       <c r="M10" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>35</v>
+        <v>23</v>
+      </c>
+      <c r="N10" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="R10" t="s">
+        <v>24</v>
       </c>
       <c r="V10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W10" t="s">
-        <v>7</v>
-      </c>
-      <c r="X10" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="Z10">
         <v>0</v>
       </c>
-      <c r="AB10" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
+      <c r="AF10" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:33">
@@ -1305,46 +1299,40 @@
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F11" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="I11" t="s">
-        <v>2</v>
-      </c>
-      <c r="J11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" t="s">
         <v>28</v>
       </c>
       <c r="M11" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>38</v>
+        <v>23</v>
+      </c>
+      <c r="N11" t="s">
+        <v>3</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="R11" t="s">
+        <v>29</v>
       </c>
       <c r="V11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W11" t="s">
-        <v>7</v>
-      </c>
-      <c r="X11" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="Z11">
         <v>0</v>
       </c>
-      <c r="AB11" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
+      <c r="AF11" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:33">
@@ -1352,46 +1340,40 @@
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F12" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I12" t="s">
-        <v>2</v>
-      </c>
-      <c r="J12" t="s">
-        <v>28</v>
+        <v>21</v>
+      </c>
+      <c r="L12" t="s">
+        <v>32</v>
       </c>
       <c r="M12" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>41</v>
+        <v>23</v>
+      </c>
+      <c r="N12" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="R12" t="s">
+        <v>33</v>
       </c>
       <c r="V12" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W12" t="s">
-        <v>7</v>
-      </c>
-      <c r="X12" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="Z12">
         <v>0</v>
       </c>
-      <c r="AB12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
+      <c r="AF12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:33">
@@ -1399,46 +1381,40 @@
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F13" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="I13" t="s">
-        <v>2</v>
-      </c>
-      <c r="J13" t="s">
-        <v>28</v>
+        <v>21</v>
+      </c>
+      <c r="L13" t="s">
+        <v>36</v>
       </c>
       <c r="M13" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>44</v>
+        <v>23</v>
+      </c>
+      <c r="N13" t="s">
+        <v>3</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="R13" t="s">
+        <v>37</v>
       </c>
       <c r="V13" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W13" t="s">
-        <v>7</v>
-      </c>
-      <c r="X13" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="Z13">
         <v>0</v>
       </c>
-      <c r="AB13" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
+      <c r="AF13" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:33">
@@ -1446,46 +1422,40 @@
         <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F14" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I14" t="s">
-        <v>2</v>
-      </c>
-      <c r="J14" t="s">
-        <v>28</v>
+        <v>21</v>
+      </c>
+      <c r="L14" t="s">
+        <v>40</v>
       </c>
       <c r="M14" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>47</v>
+        <v>23</v>
+      </c>
+      <c r="N14" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="R14" t="s">
+        <v>41</v>
       </c>
       <c r="V14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W14" t="s">
-        <v>7</v>
-      </c>
-      <c r="X14" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="Z14">
         <v>0</v>
       </c>
-      <c r="AB14" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
+      <c r="AF14" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:33">
@@ -1493,46 +1463,40 @@
         <v>14</v>
       </c>
       <c r="E15" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="I15" t="s">
-        <v>2</v>
-      </c>
-      <c r="J15" t="s">
-        <v>50</v>
+        <v>21</v>
+      </c>
+      <c r="L15" t="s">
+        <v>44</v>
       </c>
       <c r="M15" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>51</v>
+        <v>23</v>
+      </c>
+      <c r="N15" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="R15" t="s">
+        <v>45</v>
       </c>
       <c r="V15" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W15" t="s">
-        <v>7</v>
-      </c>
-      <c r="X15" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="Z15">
         <v>0</v>
       </c>
-      <c r="AB15" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE15">
-        <v>0</v>
+      <c r="AF15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:33">
@@ -1540,46 +1504,40 @@
         <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F16" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="I16" t="s">
-        <v>2</v>
-      </c>
-      <c r="J16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M16" t="s">
+        <v>23</v>
+      </c>
+      <c r="N16" t="s">
+        <v>3</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="R16" t="s">
         <v>50</v>
       </c>
-      <c r="M16" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>54</v>
-      </c>
       <c r="V16" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W16" t="s">
-        <v>7</v>
-      </c>
-      <c r="X16" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="Z16">
-        <v>77</v>
-      </c>
-      <c r="AB16" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:33">
@@ -1587,46 +1545,40 @@
         <v>16</v>
       </c>
       <c r="E17" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F17" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I17" t="s">
-        <v>2</v>
-      </c>
-      <c r="J17" t="s">
-        <v>57</v>
+        <v>48</v>
+      </c>
+      <c r="L17" t="s">
+        <v>53</v>
       </c>
       <c r="M17" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>58</v>
+        <v>23</v>
+      </c>
+      <c r="N17" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="R17" t="s">
+        <v>54</v>
       </c>
       <c r="V17" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W17" t="s">
-        <v>7</v>
-      </c>
-      <c r="X17" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="Z17">
         <v>0</v>
       </c>
-      <c r="AB17" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE17">
-        <v>0</v>
+      <c r="AF17" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:33">
@@ -1634,46 +1586,40 @@
         <v>17</v>
       </c>
       <c r="E18" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F18" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I18" t="s">
-        <v>2</v>
-      </c>
-      <c r="J18" t="s">
+        <v>48</v>
+      </c>
+      <c r="L18" t="s">
         <v>57</v>
       </c>
       <c r="M18" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>61</v>
+        <v>23</v>
+      </c>
+      <c r="N18" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="R18" t="s">
+        <v>58</v>
       </c>
       <c r="V18" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W18" t="s">
-        <v>7</v>
-      </c>
-      <c r="X18" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="Z18">
         <v>0</v>
       </c>
-      <c r="AB18" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD18" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE18">
-        <v>0</v>
+      <c r="AF18" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:33">
@@ -1681,46 +1627,40 @@
         <v>18</v>
       </c>
       <c r="E19" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" t="s">
+        <v>60</v>
+      </c>
+      <c r="I19" t="s">
+        <v>48</v>
+      </c>
+      <c r="L19" t="s">
+        <v>61</v>
+      </c>
+      <c r="M19" t="s">
+        <v>23</v>
+      </c>
+      <c r="N19" t="s">
+        <v>3</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="R19" t="s">
         <v>62</v>
       </c>
-      <c r="F19" t="s">
-        <v>63</v>
-      </c>
-      <c r="I19" t="s">
-        <v>2</v>
-      </c>
-      <c r="J19" t="s">
-        <v>57</v>
-      </c>
-      <c r="M19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>64</v>
-      </c>
       <c r="V19" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W19" t="s">
-        <v>7</v>
-      </c>
-      <c r="X19" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y19" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="Z19">
         <v>0</v>
       </c>
-      <c r="AB19" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD19" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE19">
-        <v>0</v>
+      <c r="AF19" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:33">
@@ -1728,46 +1668,40 @@
         <v>19</v>
       </c>
       <c r="E20" t="s">
+        <v>63</v>
+      </c>
+      <c r="F20" t="s">
+        <v>64</v>
+      </c>
+      <c r="I20" t="s">
+        <v>48</v>
+      </c>
+      <c r="L20" t="s">
         <v>65</v>
       </c>
-      <c r="F20" t="s">
+      <c r="M20" t="s">
+        <v>23</v>
+      </c>
+      <c r="N20" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="R20" t="s">
         <v>66</v>
       </c>
-      <c r="I20" t="s">
-        <v>2</v>
-      </c>
-      <c r="J20" t="s">
-        <v>57</v>
-      </c>
-      <c r="M20" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>67</v>
-      </c>
       <c r="V20" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W20" t="s">
-        <v>7</v>
-      </c>
-      <c r="X20" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="Z20">
         <v>0</v>
       </c>
-      <c r="AB20" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD20" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE20">
-        <v>0</v>
+      <c r="AF20" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:33">
@@ -1775,46 +1709,40 @@
         <v>20</v>
       </c>
       <c r="E21" t="s">
+        <v>67</v>
+      </c>
+      <c r="F21" t="s">
         <v>68</v>
       </c>
-      <c r="F21" t="s">
+      <c r="I21" t="s">
+        <v>48</v>
+      </c>
+      <c r="L21" t="s">
         <v>69</v>
       </c>
-      <c r="I21" t="s">
-        <v>2</v>
-      </c>
-      <c r="J21" t="s">
+      <c r="M21" t="s">
+        <v>23</v>
+      </c>
+      <c r="N21" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="R21" t="s">
         <v>70</v>
       </c>
-      <c r="M21" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>71</v>
-      </c>
       <c r="V21" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W21" t="s">
-        <v>7</v>
-      </c>
-      <c r="X21" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="Z21">
         <v>0</v>
       </c>
-      <c r="AB21" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD21" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE21">
-        <v>0</v>
+      <c r="AF21" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:33">
@@ -1822,46 +1750,40 @@
         <v>21</v>
       </c>
       <c r="E22" t="s">
+        <v>71</v>
+      </c>
+      <c r="F22" t="s">
         <v>72</v>
       </c>
-      <c r="F22" t="s">
+      <c r="I22" t="s">
+        <v>48</v>
+      </c>
+      <c r="L22" t="s">
         <v>73</v>
       </c>
-      <c r="I22" t="s">
-        <v>2</v>
-      </c>
-      <c r="J22" t="s">
-        <v>70</v>
-      </c>
       <c r="M22" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q22" t="s">
+        <v>23</v>
+      </c>
+      <c r="N22" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="R22" t="s">
         <v>74</v>
       </c>
       <c r="V22" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W22" t="s">
-        <v>7</v>
-      </c>
-      <c r="X22" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y22" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="Z22">
         <v>0</v>
       </c>
-      <c r="AB22" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD22" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE22">
-        <v>0</v>
+      <c r="AF22" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:33">
@@ -1875,40 +1797,34 @@
         <v>76</v>
       </c>
       <c r="I23" t="s">
-        <v>2</v>
-      </c>
-      <c r="J23" t="s">
-        <v>70</v>
+        <v>77</v>
+      </c>
+      <c r="L23" t="s">
+        <v>78</v>
       </c>
       <c r="M23" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>77</v>
+        <v>23</v>
+      </c>
+      <c r="N23" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="R23" t="s">
+        <v>79</v>
       </c>
       <c r="V23" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W23" t="s">
-        <v>7</v>
-      </c>
-      <c r="X23" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="Z23">
         <v>0</v>
       </c>
-      <c r="AB23" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD23" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE23">
-        <v>0</v>
+      <c r="AF23" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:33">
@@ -1916,46 +1832,40 @@
         <v>23</v>
       </c>
       <c r="E24" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I24" t="s">
-        <v>2</v>
-      </c>
-      <c r="J24" t="s">
-        <v>70</v>
+        <v>77</v>
+      </c>
+      <c r="L24" t="s">
+        <v>82</v>
       </c>
       <c r="M24" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>80</v>
+        <v>23</v>
+      </c>
+      <c r="N24" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="R24" t="s">
+        <v>83</v>
       </c>
       <c r="V24" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W24" t="s">
-        <v>7</v>
-      </c>
-      <c r="X24" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y24" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="Z24">
         <v>0</v>
       </c>
-      <c r="AB24" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD24" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE24">
-        <v>0</v>
+      <c r="AF24" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:33">
@@ -1963,46 +1873,40 @@
         <v>24</v>
       </c>
       <c r="E25" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F25" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I25" t="s">
-        <v>2</v>
-      </c>
-      <c r="J25" t="s">
-        <v>70</v>
+        <v>86</v>
+      </c>
+      <c r="L25" t="s">
+        <v>87</v>
       </c>
       <c r="M25" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>83</v>
+        <v>23</v>
+      </c>
+      <c r="N25" t="s">
+        <v>3</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="R25" t="s">
+        <v>88</v>
       </c>
       <c r="V25" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W25" t="s">
-        <v>7</v>
-      </c>
-      <c r="X25" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y25" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="Z25">
         <v>0</v>
       </c>
-      <c r="AB25" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD25" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE25">
-        <v>0</v>
+      <c r="AF25" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:33">
@@ -2010,150 +1914,457 @@
         <v>25</v>
       </c>
       <c r="E26" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F26" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I26" t="s">
-        <v>2</v>
-      </c>
-      <c r="J26" t="s">
         <v>86</v>
       </c>
+      <c r="L26" t="s">
+        <v>91</v>
+      </c>
       <c r="M26" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>87</v>
+        <v>23</v>
+      </c>
+      <c r="N26" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="R26" t="s">
+        <v>92</v>
       </c>
       <c r="V26" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W26" t="s">
-        <v>7</v>
-      </c>
-      <c r="X26" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y26" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="Z26">
         <v>0</v>
       </c>
-      <c r="AB26" t="s">
-        <v>86</v>
-      </c>
-      <c r="AD26" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE26">
-        <v>0</v>
+      <c r="AF26" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:33">
       <c r="A27">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E27" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F27" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="I27" t="s">
-        <v>2</v>
-      </c>
-      <c r="J27" t="s">
         <v>86</v>
       </c>
+      <c r="L27" t="s">
+        <v>95</v>
+      </c>
       <c r="M27" t="s">
-        <v>6</v>
-      </c>
-      <c r="P27" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>91</v>
+        <v>23</v>
+      </c>
+      <c r="N27" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="R27" t="s">
+        <v>96</v>
       </c>
       <c r="V27" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W27" t="s">
-        <v>7</v>
-      </c>
-      <c r="X27" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y27" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="Z27">
         <v>0</v>
       </c>
-      <c r="AB27" t="s">
-        <v>86</v>
-      </c>
-      <c r="AD27" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE27">
-        <v>0</v>
+      <c r="AF27" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:33">
       <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="E28" t="s">
+        <v>97</v>
+      </c>
+      <c r="F28" t="s">
+        <v>98</v>
+      </c>
+      <c r="I28" t="s">
+        <v>86</v>
+      </c>
+      <c r="L28" t="s">
+        <v>99</v>
+      </c>
+      <c r="M28" t="s">
+        <v>23</v>
+      </c>
+      <c r="N28" t="s">
+        <v>3</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="R28" t="s">
+        <v>100</v>
+      </c>
+      <c r="V28" t="s">
+        <v>3</v>
+      </c>
+      <c r="W28" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="E29" t="s">
+        <v>101</v>
+      </c>
+      <c r="F29" t="s">
+        <v>102</v>
+      </c>
+      <c r="I29" t="s">
+        <v>103</v>
+      </c>
+      <c r="L29" t="s">
+        <v>104</v>
+      </c>
+      <c r="M29" t="s">
+        <v>23</v>
+      </c>
+      <c r="N29" t="s">
+        <v>3</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="R29" t="s">
+        <v>105</v>
+      </c>
+      <c r="V29" t="s">
+        <v>3</v>
+      </c>
+      <c r="W29" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="E30" t="s">
+        <v>106</v>
+      </c>
+      <c r="F30" t="s">
+        <v>107</v>
+      </c>
+      <c r="I30" t="s">
+        <v>103</v>
+      </c>
+      <c r="L30" t="s">
+        <v>108</v>
+      </c>
+      <c r="M30" t="s">
+        <v>23</v>
+      </c>
+      <c r="N30" t="s">
+        <v>3</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="R30" t="s">
+        <v>109</v>
+      </c>
+      <c r="V30" t="s">
+        <v>3</v>
+      </c>
+      <c r="W30" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="E31" t="s">
+        <v>110</v>
+      </c>
+      <c r="F31" t="s">
+        <v>111</v>
+      </c>
+      <c r="I31" t="s">
+        <v>103</v>
+      </c>
+      <c r="L31" t="s">
+        <v>112</v>
+      </c>
+      <c r="M31" t="s">
+        <v>23</v>
+      </c>
+      <c r="N31" t="s">
+        <v>3</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="R31" t="s">
+        <v>113</v>
+      </c>
+      <c r="V31" t="s">
+        <v>3</v>
+      </c>
+      <c r="W31" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33">
+      <c r="A32">
         <v>31</v>
       </c>
-      <c r="E28" t="s">
-        <v>84</v>
-      </c>
-      <c r="F28" t="s">
-        <v>92</v>
-      </c>
-      <c r="I28" t="s">
-        <v>2</v>
-      </c>
-      <c r="J28" t="s">
-        <v>93</v>
-      </c>
-      <c r="M28" t="s">
-        <v>6</v>
-      </c>
-      <c r="P28" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>87</v>
-      </c>
-      <c r="V28" t="s">
-        <v>6</v>
-      </c>
-      <c r="W28" t="s">
-        <v>7</v>
-      </c>
-      <c r="X28" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y28" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z28">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="s">
-        <v>94</v>
-      </c>
-      <c r="AD28" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE28">
-        <v>0</v>
+      <c r="E32" t="s">
+        <v>114</v>
+      </c>
+      <c r="F32" t="s">
+        <v>115</v>
+      </c>
+      <c r="I32" t="s">
+        <v>103</v>
+      </c>
+      <c r="L32" t="s">
+        <v>116</v>
+      </c>
+      <c r="M32" t="s">
+        <v>23</v>
+      </c>
+      <c r="N32" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="R32" t="s">
+        <v>117</v>
+      </c>
+      <c r="V32" t="s">
+        <v>3</v>
+      </c>
+      <c r="W32" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:33">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="E33" t="s">
+        <v>118</v>
+      </c>
+      <c r="F33" t="s">
+        <v>119</v>
+      </c>
+      <c r="I33" t="s">
+        <v>103</v>
+      </c>
+      <c r="L33" t="s">
+        <v>120</v>
+      </c>
+      <c r="M33" t="s">
+        <v>23</v>
+      </c>
+      <c r="N33" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="R33" t="s">
+        <v>121</v>
+      </c>
+      <c r="V33" t="s">
+        <v>3</v>
+      </c>
+      <c r="W33" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:33">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="E34" t="s">
+        <v>122</v>
+      </c>
+      <c r="F34" t="s">
+        <v>123</v>
+      </c>
+      <c r="I34" t="s">
+        <v>124</v>
+      </c>
+      <c r="L34" t="s">
+        <v>125</v>
+      </c>
+      <c r="M34" t="s">
+        <v>23</v>
+      </c>
+      <c r="N34" t="s">
+        <v>3</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="R34" t="s">
+        <v>126</v>
+      </c>
+      <c r="V34" t="s">
+        <v>3</v>
+      </c>
+      <c r="W34" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:33">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="E35" t="s">
+        <v>127</v>
+      </c>
+      <c r="F35" t="s">
+        <v>128</v>
+      </c>
+      <c r="I35" t="s">
+        <v>124</v>
+      </c>
+      <c r="K35" t="s">
+        <v>129</v>
+      </c>
+      <c r="L35" t="s">
+        <v>130</v>
+      </c>
+      <c r="M35" t="s">
+        <v>23</v>
+      </c>
+      <c r="N35" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="R35" t="s">
+        <v>131</v>
+      </c>
+      <c r="V35" t="s">
+        <v>3</v>
+      </c>
+      <c r="W35" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="E36" t="s">
+        <v>122</v>
+      </c>
+      <c r="F36" t="s">
+        <v>132</v>
+      </c>
+      <c r="I36" t="s">
+        <v>133</v>
+      </c>
+      <c r="L36" t="s">
+        <v>125</v>
+      </c>
+      <c r="M36" t="s">
+        <v>23</v>
+      </c>
+      <c r="N36" t="s">
+        <v>3</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="R36" t="s">
+        <v>134</v>
+      </c>
+      <c r="V36" t="s">
+        <v>3</v>
+      </c>
+      <c r="W36" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AG1" xr:uid="{372403934-0777-4c37-8910-a4cd1c3726ff}"/>
+  <autoFilter ref="A1:AG1" xr:uid="{3036bd9e9-23b9-4345-b53b-ec941b639a77}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/event.xlsx
+++ b/event.xlsx
@@ -1,8 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\PBL smt 4\sisc\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E323977F-E1D3-4EA4-AF88-7E7D9104D8A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="event" sheetId="1" r:id="rId1"/>
   </sheets>
@@ -11,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="168">
   <si>
     <t>Polines</t>
   </si>
@@ -202,7 +211,7 @@
     <t>2026-05-05 00:44:52.671362</t>
   </si>
   <si>
-    <t>The 7th Annual International Conference and Exhibition on Indonesian Medical Education and Research </t>
+    <t>The 7th Annual International Conference and Exhibition on Indonesian Medical Education and Research</t>
   </si>
   <si>
     <t>the-7th-annual-international-conference-and-exhibition-on-indonesian-medical-education-and-research-</t>
@@ -416,17 +425,111 @@
   </si>
   <si>
     <t>2026-05-05 00:44:52.727008</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>organizer_id</t>
+  </si>
+  <si>
+    <t>kategori_id</t>
+  </si>
+  <si>
+    <t>kota_id</t>
+  </si>
+  <si>
+    <t>judul</t>
+  </si>
+  <si>
+    <t>slug</t>
+  </si>
+  <si>
+    <t>deskripsi</t>
+  </si>
+  <si>
+    <t>banner_url</t>
+  </si>
+  <si>
+    <t>tanggal_mulai</t>
+  </si>
+  <si>
+    <t>tanggal_selesai</t>
+  </si>
+  <si>
+    <t>detail_lokasi</t>
+  </si>
+  <si>
+    <t>link_eksternal</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>hasil_scraping</t>
+  </si>
+  <si>
+    <t>website_sumber</t>
+  </si>
+  <si>
+    <t>jumlah_tayangan</t>
+  </si>
+  <si>
+    <t>alasan_penolakan</t>
+  </si>
+  <si>
+    <t>dibuat_pada</t>
+  </si>
+  <si>
+    <t>diperbarui_pada</t>
+  </si>
+  <si>
+    <t>syarat_dan_ketentuan</t>
+  </si>
+  <si>
+    <t>batas_registrasi</t>
+  </si>
+  <si>
+    <t>is_event_polines</t>
+  </si>
+  <si>
+    <t>jenis_event</t>
+  </si>
+  <si>
+    <t>tipe_platform</t>
+  </si>
+  <si>
+    <t>tipe_harga</t>
+  </si>
+  <si>
+    <t>harga</t>
+  </si>
+  <si>
+    <t>nama_kontak</t>
+  </si>
+  <si>
+    <t>email_kontak</t>
+  </si>
+  <si>
+    <t>telepon_kontak</t>
+  </si>
+  <si>
+    <t>kuota</t>
+  </si>
+  <si>
+    <t>maks_tiket_per_transaksi</t>
+  </si>
+  <si>
+    <t>satu_akun_satu_transaksi</t>
+  </si>
+  <si>
+    <t>dihapus_pada</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="166" formatCode="h:mm:ss"/>
-  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
@@ -444,9 +547,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="1">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="2">
@@ -470,14 +576,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -791,16 +894,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ce6fc980-44b3-410f-982f-1b5ec58c0834}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE6FC980-44B3-410F-982F-1B5EC58C0834}">
   <dimension ref="A1:AG36"/>
-  <sheetFormatPr baseColWidth="12" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="13.140625" defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="50" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="50" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="50" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="28" bestFit="1" customWidth="1"/>
@@ -808,15 +910,13 @@
     <col min="11" max="11" width="20" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="50" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="20" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="21" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="22" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="31" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="21" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="26" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="22" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="22" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="22" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="17" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="19" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="15" bestFit="1" customWidth="1"/>
@@ -825,181 +925,123 @@
     <col min="28" max="28" width="18" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="10" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="31" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="31" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="31" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33">
-      <c r="A1" t="inlineStr" s="1">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr" s="1">
-        <is>
-          <t>organizer_id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr" s="1">
-        <is>
-          <t>kategori_id</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr" s="1">
-        <is>
-          <t>kota_id</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr" s="1">
-        <is>
-          <t>judul</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr" s="1">
-        <is>
-          <t>slug</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr" s="1">
-        <is>
-          <t>deskripsi</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr" s="1">
-        <is>
-          <t>banner_url</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr" s="1">
-        <is>
-          <t>tanggal_mulai</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr" s="1">
-        <is>
-          <t>tanggal_selesai</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr" s="1">
-        <is>
-          <t>detail_lokasi</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr" s="1">
-        <is>
-          <t>link_eksternal</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr" s="1">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr" s="1">
-        <is>
-          <t>hasil_scraping</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr" s="1">
-        <is>
-          <t>website_sumber</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr" s="1">
-        <is>
-          <t>jumlah_tayangan</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr" s="1">
-        <is>
-          <t>alasan_penolakan</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr" s="1">
-        <is>
-          <t>dibuat_pada</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr" s="1">
-        <is>
-          <t>diperbarui_pada</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr" s="1">
-        <is>
-          <t>syarat_dan_ketentuan</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr" s="1">
-        <is>
-          <t>batas_registrasi</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr" s="1">
-        <is>
-          <t>is_event_polines</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr" s="1">
-        <is>
-          <t>jenis_event</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr" s="1">
-        <is>
-          <t>tipe_platform</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr" s="1">
-        <is>
-          <t>tipe_harga</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr" s="1">
-        <is>
-          <t>harga</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr" s="1">
-        <is>
-          <t>nama_kontak</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr" s="1">
-        <is>
-          <t>email_kontak</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr" s="1">
-        <is>
-          <t>telepon_kontak</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr" s="1">
-        <is>
-          <t>kuota</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr" s="1">
-        <is>
-          <t>maks_tiket_per_transaksi</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr" s="1">
-        <is>
-          <t>satu_akun_satu_transaksi</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr" s="1">
-        <is>
-          <t>dihapus_pada</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" spans="1:33">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
@@ -1029,8 +1071,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:33">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.45">
       <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
         <v>2</v>
       </c>
       <c r="E3" t="s">
@@ -1061,9 +1112,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:33">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1093,10 +1153,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:33">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>4</v>
       </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
       <c r="E5" t="s">
         <v>12</v>
       </c>
@@ -1125,10 +1194,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:33">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>5</v>
       </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
       <c r="E6" t="s">
         <v>0</v>
       </c>
@@ -1157,10 +1235,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:33">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>6</v>
       </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
       <c r="E7" t="s">
         <v>6</v>
       </c>
@@ -1189,10 +1276,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:33">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>7</v>
       </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
@@ -1221,10 +1317,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:33">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>8</v>
       </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
       <c r="E9" t="s">
         <v>12</v>
       </c>
@@ -1253,10 +1358,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:33">
+    <row r="10" spans="1:33" ht="37" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>9</v>
       </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
       <c r="E10" t="s">
         <v>19</v>
       </c>
@@ -1294,10 +1408,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:33">
+    <row r="11" spans="1:33" ht="37" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>10</v>
       </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
       <c r="E11" t="s">
         <v>26</v>
       </c>
@@ -1335,10 +1458,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:33">
+    <row r="12" spans="1:33" ht="37" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>11</v>
       </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
       <c r="E12" t="s">
         <v>30</v>
       </c>
@@ -1376,10 +1508,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:33">
+    <row r="13" spans="1:33" ht="37" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>12</v>
       </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
       <c r="E13" t="s">
         <v>34</v>
       </c>
@@ -1417,10 +1558,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:33">
+    <row r="14" spans="1:33" ht="37" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>13</v>
       </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
       <c r="E14" t="s">
         <v>38</v>
       </c>
@@ -1458,10 +1608,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:33">
+    <row r="15" spans="1:33" ht="37" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>14</v>
       </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
       <c r="E15" t="s">
         <v>42</v>
       </c>
@@ -1499,10 +1658,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:33">
+    <row r="16" spans="1:33" ht="37" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>15</v>
       </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
       <c r="E16" t="s">
         <v>46</v>
       </c>
@@ -1540,10 +1708,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:33">
+    <row r="17" spans="1:32" ht="37" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>16</v>
       </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
       <c r="E17" t="s">
         <v>51</v>
       </c>
@@ -1581,10 +1755,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:33">
+    <row r="18" spans="1:32" ht="37" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>17</v>
       </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>2</v>
+      </c>
       <c r="E18" t="s">
         <v>55</v>
       </c>
@@ -1622,10 +1805,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:33">
+    <row r="19" spans="1:32" ht="37" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>18</v>
       </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
       <c r="E19" t="s">
         <v>59</v>
       </c>
@@ -1663,10 +1852,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:33">
+    <row r="20" spans="1:32" ht="55.5" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>19</v>
       </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
       <c r="E20" t="s">
         <v>63</v>
       </c>
@@ -1704,10 +1902,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:33">
+    <row r="21" spans="1:32" ht="37" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>20</v>
       </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
       <c r="E21" t="s">
         <v>67</v>
       </c>
@@ -1745,10 +1952,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:33">
+    <row r="22" spans="1:32" ht="37" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>21</v>
       </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
       <c r="E22" t="s">
         <v>71</v>
       </c>
@@ -1786,10 +1999,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:33">
+    <row r="23" spans="1:32" ht="37" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>22</v>
       </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
       <c r="E23" t="s">
         <v>75</v>
       </c>
@@ -1827,10 +2049,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:33">
+    <row r="24" spans="1:32" ht="37" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>23</v>
       </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
       <c r="E24" t="s">
         <v>80</v>
       </c>
@@ -1868,10 +2099,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:33">
+    <row r="25" spans="1:32" ht="37" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>24</v>
       </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
       <c r="E25" t="s">
         <v>84</v>
       </c>
@@ -1909,10 +2149,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:33">
+    <row r="26" spans="1:32" ht="37" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>25</v>
       </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>2</v>
+      </c>
       <c r="E26" t="s">
         <v>89</v>
       </c>
@@ -1950,10 +2199,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:33">
+    <row r="27" spans="1:32" ht="37" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>26</v>
       </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
       <c r="E27" t="s">
         <v>93</v>
       </c>
@@ -1991,10 +2249,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:33">
+    <row r="28" spans="1:32" ht="37" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>27</v>
       </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>2</v>
+      </c>
       <c r="E28" t="s">
         <v>97</v>
       </c>
@@ -2032,10 +2299,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:33">
+    <row r="29" spans="1:32" ht="37" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>28</v>
       </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29">
+        <v>2</v>
+      </c>
       <c r="E29" t="s">
         <v>101</v>
       </c>
@@ -2073,10 +2349,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:33">
+    <row r="30" spans="1:32" ht="37" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>29</v>
       </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>2</v>
+      </c>
       <c r="E30" t="s">
         <v>106</v>
       </c>
@@ -2114,10 +2399,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:33">
+    <row r="31" spans="1:32" ht="37" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>30</v>
       </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
       <c r="E31" t="s">
         <v>110</v>
       </c>
@@ -2155,10 +2449,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:33">
+    <row r="32" spans="1:32" ht="37" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>31</v>
       </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
       <c r="E32" t="s">
         <v>114</v>
       </c>
@@ -2196,10 +2496,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:33">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>32</v>
       </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>2</v>
+      </c>
       <c r="E33" t="s">
         <v>118</v>
       </c>
@@ -2237,10 +2546,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:33">
+    <row r="34" spans="1:32" ht="37" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>33</v>
       </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34">
+        <v>2</v>
+      </c>
       <c r="E34" t="s">
         <v>122</v>
       </c>
@@ -2278,10 +2596,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:33">
+    <row r="35" spans="1:32" ht="37" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>34</v>
       </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>2</v>
+      </c>
       <c r="E35" t="s">
         <v>127</v>
       </c>
@@ -2322,10 +2649,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:33">
+    <row r="36" spans="1:32" ht="37" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>35</v>
       </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36">
+        <v>2</v>
+      </c>
       <c r="E36" t="s">
         <v>122</v>
       </c>
@@ -2364,7 +2700,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AG1" xr:uid="{3036bd9e9-23b9-4345-b53b-ec941b639a77}"/>
+  <autoFilter ref="A1:AG1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>